--- a/02_data_contract.xlsx
+++ b/02_data_contract.xlsx
@@ -4,7 +4,7 @@
   <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data Contract" sheetId="1" state="visible" r:id="rId2"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <si>
     <t>Dataset</t>
   </si>
@@ -438,15 +438,6 @@
     <t xml:space="preserve">Matches the rate AstraPay actually realizes when currency actually converts. 'card_network' carries an unrelated card-scheme markup; 'interbank' is an indicative reporting rate only.</t>
   </si>
   <si>
-    <t xml:space="preserve">FX conversion — indicative/attempted GPV in USD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">created_at, rate_type = 'interbank'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gives a same-day, mark-to-market view of attempted volume before any settlement record exists.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fraud / chargeback cost attribution</t>
   </si>
   <si>
@@ -457,18 +448,6 @@
   </si>
   <si>
     <t xml:space="preserve">Attributes the economic event to the month it originated, not the month the dispute was filed (chargebacks can open weeks or months later). opened_at is still tracked separately for dispute-aging/operational KPIs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data freshness / pipeline SLA</t>
-  </si>
-  <si>
-    <t>ingestion_time</t>
-  </si>
-  <si>
-    <t>payment_event</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is a system/pipeline question, not a business date — never substitute it into a business KPI.</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1473,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="3" style="0" width="34"/>
     <col customWidth="1" min="4" max="4" style="0" width="70"/>
@@ -1606,39 +1585,17 @@
         <v>140</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>149</v>
-      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
